--- a/Battery/Polly-display.xlsx
+++ b/Battery/Polly-display.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yaoyitong/Documents/Pollyyaooo-Polly_514_Final/Battery/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yaoyitong/Documents/Pollyyaooo-Polly_514_Final/battery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DB04F78-B31C-0A41-9F80-30B95D0177E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8573F10-F1EE-FA44-B771-C8F6BA4BF3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1203,10 +1203,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -1407,7 +1403,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2024,7 +2019,7 @@
     <hyperlink ref="A11" r:id="rId3" xr:uid="{5D9F9F67-9699-49D7-BADD-F38BCBFDD77B}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId4"/>
 </worksheet>
 </file>
